--- a/apps/bottleneck-breakthrough/Cool_Hollow_Coaching_Milestone_6_Bottleneck_Breakthrough_Template.xlsx
+++ b/apps/bottleneck-breakthrough/Cool_Hollow_Coaching_Milestone_6_Bottleneck_Breakthrough_Template.xlsx
@@ -35,17 +35,17 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="00E8C766"/>
       <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="000E4643"/>
+      <color rgb="001A1A1A"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="000E4643"/>
+      <color rgb="001A1A1A"/>
       <sz val="11"/>
     </font>
     <font>
@@ -56,7 +56,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="000E4643"/>
+      <color rgb="001A1A1A"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -74,11 +74,11 @@
       <name val="Calibri"/>
       <b val="1"/>
       <i val="1"/>
-      <color rgb="000E4643"/>
+      <color rgb="001A1A1A"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -87,12 +87,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000E4643"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00589BA8"/>
+        <fgColor rgb="001A1A1A"/>
       </patternFill>
     </fill>
     <fill>
@@ -102,12 +97,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00B4D351"/>
+        <fgColor rgb="00E8C766"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FAF8F3"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -149,19 +144,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>

--- a/apps/bottleneck-breakthrough/Cool_Hollow_Coaching_Milestone_6_Bottleneck_Breakthrough_Template.xlsx
+++ b/apps/bottleneck-breakthrough/Cool_Hollow_Coaching_Milestone_6_Bottleneck_Breakthrough_Template.xlsx
@@ -8,7 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Constraint Worksheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Examples" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Starter Ideas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Constraint Worksheet" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,8 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="10">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,12 +43,32 @@
       <sz val="12"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="001A1A1A"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="001A1A1A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="005A5A5A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="001A1A1A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="001A1A1A"/>
       <sz val="11"/>
     </font>
@@ -61,21 +85,8 @@
     <font>
       <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="005A5A5A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
       <color rgb="006B6B6B"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <i val="1"/>
-      <color rgb="001A1A1A"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -92,12 +103,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EFEFEF"/>
+        <fgColor rgb="00E8C766"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8C766"/>
+        <fgColor rgb="00EFEFEF"/>
       </patternFill>
     </fill>
     <fill>
@@ -132,11 +143,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -144,19 +156,30 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -519,10 +542,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001A1A1A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -535,137 +559,156 @@
           <t>Cool Hollow Coaching · Business Without You</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Milestone 6: The Bottleneck Breakthrough Plan</t>
         </is>
       </c>
+      <c r="B2" s="2" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>How to use this template</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>List every candidate constraint across your three mapped processes. The tool ranks them all, names the single binding constraint to break first, and builds a separate automation hit list ranked by effort-adjusted payoff.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="6" ht="68" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>List every candidate constraint across your three mapped processes. The tool ranks them all, names the single binding constraint to break first, and builds a separate automation hit list ranked by effort-adjusted payoff. The Starter Ideas tab lists the constraints we see most often, use it to jog your memory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Three steps: fill in the data tab(s), save this file, then upload this same file into the tool. The Examples and Starter Ideas tabs are for reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>The tool never reads them, only type your real data on the data tab(s).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>On the "Constraint Worksheet" tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>What to put here</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Constraint Name</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>One row per candidate constraint from your Constraint Identification worksheet.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Which of your three mapped processes this constraint sits in.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Frequency Per Week</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>How many times a week this constraint actually bites.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Hours Lost Per Occurrence</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Hours lost each time it happens.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Hours lost each time it happens. Decimals are fine, 30 minutes is 0.5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Downstream Impact</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>1 to 5. How much this blocks everything else in the business.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>Automatable</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>yes or no.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>Automation Effort</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>1 to 5, only matters if Automatable is yes. 1 is trivial, 5 is hard.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Fill in the data tab, save the file, then upload it straight into the tool.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="6">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A8:B8"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -674,10 +717,398 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="006B6B6B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cool Hollow Coaching · Business Without You</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Milestone 6: The Bottleneck Breakthrough Plan</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="6" customHeight="1"/>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Filled-in examples, for reference only. Type your own data on the data tab(s), not here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>The tool never reads this tab, anything you type here is ignored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Example for the "Constraint Worksheet" tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Constraint Name</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Frequency Per Week</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Hours Lost Per Occurrence</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Downstream Impact</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>Automatable</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>Automation Effort</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Owner approves every quote before it goes out</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Only one person knows how to run delivery scheduling</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Invoices assembled by hand from job notes</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Billing</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A5:G5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00E8C766"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cool Hollow Coaching · Business Without You</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Milestone 6: The Bottleneck Breakthrough Plan</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="6" customHeight="1"/>
+    <row r="4" ht="44" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>The most common answers we see across owner-run businesses. Copy any that are true for yours onto the data tab, reworded to match how your business actually runs, then fill in the numbers and ratings yourself, honestly. Don't copy anything that isn't real for you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>The tool never reads this tab, copy items onto the data tab to use them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>The owner is the constraint</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Owner approves every quote before it goes out</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Waiting on the owner for pricing decisions</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Every problem escalates to the owner instead of getting solved</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Owner is the only one who talks to key customers</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Knowledge lives in one head</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Only one person knows how to run scheduling</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>No documented onboarding for new hires</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>Job details live in one person's head or notebook</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Only one person can quote complex work</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Manual work that slows everything</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Invoices assembled by hand from job notes</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Payments collected manually after the job</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>Materials ordered only when someone notices they're low</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>Jobs scheduled on a whiteboard or by phone calls</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Same customer questions answered one at a time, from scratch</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A12:B12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C8A227"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -695,447 +1126,438 @@
           <t>Cool Hollow Coaching · Business Without You</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Milestone 6: The Bottleneck Breakthrough Plan</t>
         </is>
       </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Constraint Name</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Frequency Per Week</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>Hours Lost Per Occurrence</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>Downstream Impact</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Automatable</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>Automation Effort</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Owner approves every quote before it goes out</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="A5" s="15" t="n"/>
+      <c r="B5" s="15" t="n"/>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="16" t="n"/>
+      <c r="F5" s="15" t="n"/>
+      <c r="G5" s="16" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Only one person knows how to run delivery scheduling</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Your data starts here, replace or delete the example rows above</t>
-        </is>
-      </c>
+      <c r="A6" s="15" t="n"/>
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="16" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="16" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="n"/>
+      <c r="B7" s="15" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="15" t="n"/>
+      <c r="G7" s="16" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n"/>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
+      <c r="A8" s="15" t="n"/>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="16" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="16" t="n"/>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="16" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="n"/>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="11" t="n"/>
+      <c r="A9" s="15" t="n"/>
+      <c r="B9" s="15" t="n"/>
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="16" t="n"/>
+      <c r="F9" s="15" t="n"/>
+      <c r="G9" s="16" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n"/>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="11" t="n"/>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="n"/>
+      <c r="A10" s="15" t="n"/>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="16" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n"/>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="11" t="n"/>
+      <c r="A11" s="15" t="n"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="15" t="n"/>
+      <c r="G11" s="16" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
+      <c r="A12" s="15" t="n"/>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="15" t="n"/>
+      <c r="G12" s="16" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n"/>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="11" t="n"/>
-      <c r="G13" s="11" t="n"/>
+      <c r="A13" s="15" t="n"/>
+      <c r="B13" s="15" t="n"/>
+      <c r="C13" s="16" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="16" t="n"/>
+      <c r="F13" s="15" t="n"/>
+      <c r="G13" s="16" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n"/>
-      <c r="B14" s="11" t="n"/>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="11" t="n"/>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
+      <c r="A14" s="15" t="n"/>
+      <c r="B14" s="15" t="n"/>
+      <c r="C14" s="16" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="16" t="n"/>
+      <c r="F14" s="15" t="n"/>
+      <c r="G14" s="16" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="n"/>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
+      <c r="A15" s="15" t="n"/>
+      <c r="B15" s="15" t="n"/>
+      <c r="C15" s="16" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="16" t="n"/>
+      <c r="F15" s="15" t="n"/>
+      <c r="G15" s="16" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n"/>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
+      <c r="A16" s="15" t="n"/>
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="16" t="n"/>
+      <c r="F16" s="15" t="n"/>
+      <c r="G16" s="16" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="n"/>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="11" t="n"/>
-      <c r="G17" s="11" t="n"/>
+      <c r="A17" s="15" t="n"/>
+      <c r="B17" s="15" t="n"/>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="15" t="n"/>
+      <c r="G17" s="16" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n"/>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="11" t="n"/>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
+      <c r="A18" s="15" t="n"/>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="16" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="16" t="n"/>
+      <c r="F18" s="15" t="n"/>
+      <c r="G18" s="16" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="n"/>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="11" t="n"/>
-      <c r="G19" s="11" t="n"/>
+      <c r="A19" s="15" t="n"/>
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="16" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="16" t="n"/>
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="16" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="n"/>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
+      <c r="A20" s="15" t="n"/>
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="16" t="n"/>
+      <c r="F20" s="15" t="n"/>
+      <c r="G20" s="16" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="n"/>
-      <c r="B21" s="11" t="n"/>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="11" t="n"/>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="11" t="n"/>
-      <c r="G21" s="11" t="n"/>
+      <c r="A21" s="15" t="n"/>
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="16" t="n"/>
+      <c r="F21" s="15" t="n"/>
+      <c r="G21" s="16" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="n"/>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="11" t="n"/>
-      <c r="G22" s="11" t="n"/>
+      <c r="A22" s="15" t="n"/>
+      <c r="B22" s="15" t="n"/>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="16" t="n"/>
+      <c r="F22" s="15" t="n"/>
+      <c r="G22" s="16" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="n"/>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="11" t="n"/>
-      <c r="F23" s="11" t="n"/>
-      <c r="G23" s="11" t="n"/>
+      <c r="A23" s="15" t="n"/>
+      <c r="B23" s="15" t="n"/>
+      <c r="C23" s="16" t="n"/>
+      <c r="D23" s="17" t="n"/>
+      <c r="E23" s="16" t="n"/>
+      <c r="F23" s="15" t="n"/>
+      <c r="G23" s="16" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="n"/>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="11" t="n"/>
-      <c r="E24" s="11" t="n"/>
-      <c r="F24" s="11" t="n"/>
-      <c r="G24" s="11" t="n"/>
+      <c r="A24" s="15" t="n"/>
+      <c r="B24" s="15" t="n"/>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="16" t="n"/>
+      <c r="F24" s="15" t="n"/>
+      <c r="G24" s="16" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n"/>
-      <c r="B25" s="11" t="n"/>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="11" t="n"/>
-      <c r="E25" s="11" t="n"/>
-      <c r="F25" s="11" t="n"/>
-      <c r="G25" s="11" t="n"/>
+      <c r="A25" s="15" t="n"/>
+      <c r="B25" s="15" t="n"/>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="16" t="n"/>
+      <c r="F25" s="15" t="n"/>
+      <c r="G25" s="16" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="n"/>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="11" t="n"/>
-      <c r="F26" s="11" t="n"/>
-      <c r="G26" s="11" t="n"/>
+      <c r="A26" s="15" t="n"/>
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="16" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="16" t="n"/>
+      <c r="F26" s="15" t="n"/>
+      <c r="G26" s="16" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="n"/>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="11" t="n"/>
-      <c r="E27" s="11" t="n"/>
-      <c r="F27" s="11" t="n"/>
-      <c r="G27" s="11" t="n"/>
+      <c r="A27" s="15" t="n"/>
+      <c r="B27" s="15" t="n"/>
+      <c r="C27" s="16" t="n"/>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="16" t="n"/>
+      <c r="F27" s="15" t="n"/>
+      <c r="G27" s="16" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="n"/>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="11" t="n"/>
-      <c r="F28" s="11" t="n"/>
-      <c r="G28" s="11" t="n"/>
+      <c r="A28" s="15" t="n"/>
+      <c r="B28" s="15" t="n"/>
+      <c r="C28" s="16" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="16" t="n"/>
+      <c r="F28" s="15" t="n"/>
+      <c r="G28" s="16" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="n"/>
-      <c r="B29" s="11" t="n"/>
-      <c r="C29" s="11" t="n"/>
-      <c r="D29" s="11" t="n"/>
-      <c r="E29" s="11" t="n"/>
-      <c r="F29" s="11" t="n"/>
-      <c r="G29" s="11" t="n"/>
+      <c r="A29" s="15" t="n"/>
+      <c r="B29" s="15" t="n"/>
+      <c r="C29" s="16" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="16" t="n"/>
+      <c r="F29" s="15" t="n"/>
+      <c r="G29" s="16" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="n"/>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="11" t="n"/>
-      <c r="F30" s="11" t="n"/>
-      <c r="G30" s="11" t="n"/>
+      <c r="A30" s="15" t="n"/>
+      <c r="B30" s="15" t="n"/>
+      <c r="C30" s="16" t="n"/>
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="16" t="n"/>
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="16" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="n"/>
-      <c r="B31" s="11" t="n"/>
-      <c r="C31" s="11" t="n"/>
-      <c r="D31" s="11" t="n"/>
-      <c r="E31" s="11" t="n"/>
-      <c r="F31" s="11" t="n"/>
-      <c r="G31" s="11" t="n"/>
+      <c r="A31" s="15" t="n"/>
+      <c r="B31" s="15" t="n"/>
+      <c r="C31" s="16" t="n"/>
+      <c r="D31" s="17" t="n"/>
+      <c r="E31" s="16" t="n"/>
+      <c r="F31" s="15" t="n"/>
+      <c r="G31" s="16" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="n"/>
-      <c r="B32" s="11" t="n"/>
-      <c r="C32" s="11" t="n"/>
-      <c r="D32" s="11" t="n"/>
-      <c r="E32" s="11" t="n"/>
-      <c r="F32" s="11" t="n"/>
-      <c r="G32" s="11" t="n"/>
+      <c r="A32" s="15" t="n"/>
+      <c r="B32" s="15" t="n"/>
+      <c r="C32" s="16" t="n"/>
+      <c r="D32" s="17" t="n"/>
+      <c r="E32" s="16" t="n"/>
+      <c r="F32" s="15" t="n"/>
+      <c r="G32" s="16" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="n"/>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="11" t="n"/>
-      <c r="D33" s="11" t="n"/>
-      <c r="E33" s="11" t="n"/>
-      <c r="F33" s="11" t="n"/>
-      <c r="G33" s="11" t="n"/>
+      <c r="A33" s="15" t="n"/>
+      <c r="B33" s="15" t="n"/>
+      <c r="C33" s="16" t="n"/>
+      <c r="D33" s="17" t="n"/>
+      <c r="E33" s="16" t="n"/>
+      <c r="F33" s="15" t="n"/>
+      <c r="G33" s="16" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="n"/>
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="11" t="n"/>
-      <c r="D34" s="11" t="n"/>
-      <c r="E34" s="11" t="n"/>
-      <c r="F34" s="11" t="n"/>
-      <c r="G34" s="11" t="n"/>
+      <c r="A34" s="15" t="n"/>
+      <c r="B34" s="15" t="n"/>
+      <c r="C34" s="16" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="16" t="n"/>
+      <c r="F34" s="15" t="n"/>
+      <c r="G34" s="16" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="n"/>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="11" t="n"/>
-      <c r="D35" s="11" t="n"/>
-      <c r="E35" s="11" t="n"/>
-      <c r="F35" s="11" t="n"/>
-      <c r="G35" s="11" t="n"/>
+      <c r="A35" s="15" t="n"/>
+      <c r="B35" s="15" t="n"/>
+      <c r="C35" s="16" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="16" t="n"/>
+      <c r="F35" s="15" t="n"/>
+      <c r="G35" s="16" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="n"/>
-      <c r="B36" s="11" t="n"/>
-      <c r="C36" s="11" t="n"/>
-      <c r="D36" s="11" t="n"/>
-      <c r="E36" s="11" t="n"/>
-      <c r="F36" s="11" t="n"/>
-      <c r="G36" s="11" t="n"/>
+      <c r="A36" s="15" t="n"/>
+      <c r="B36" s="15" t="n"/>
+      <c r="C36" s="16" t="n"/>
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="16" t="n"/>
+      <c r="F36" s="15" t="n"/>
+      <c r="G36" s="16" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="n"/>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="11" t="n"/>
-      <c r="D37" s="11" t="n"/>
-      <c r="E37" s="11" t="n"/>
-      <c r="F37" s="11" t="n"/>
-      <c r="G37" s="11" t="n"/>
+      <c r="A37" s="15" t="n"/>
+      <c r="B37" s="15" t="n"/>
+      <c r="C37" s="16" t="n"/>
+      <c r="D37" s="17" t="n"/>
+      <c r="E37" s="16" t="n"/>
+      <c r="F37" s="15" t="n"/>
+      <c r="G37" s="16" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="n"/>
-      <c r="B38" s="11" t="n"/>
-      <c r="C38" s="11" t="n"/>
-      <c r="D38" s="11" t="n"/>
-      <c r="E38" s="11" t="n"/>
-      <c r="F38" s="11" t="n"/>
-      <c r="G38" s="11" t="n"/>
+      <c r="A38" s="15" t="n"/>
+      <c r="B38" s="15" t="n"/>
+      <c r="C38" s="16" t="n"/>
+      <c r="D38" s="17" t="n"/>
+      <c r="E38" s="16" t="n"/>
+      <c r="F38" s="15" t="n"/>
+      <c r="G38" s="16" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="n"/>
-      <c r="B39" s="11" t="n"/>
-      <c r="C39" s="11" t="n"/>
-      <c r="D39" s="11" t="n"/>
-      <c r="E39" s="11" t="n"/>
-      <c r="F39" s="11" t="n"/>
-      <c r="G39" s="11" t="n"/>
+      <c r="A39" s="15" t="n"/>
+      <c r="B39" s="15" t="n"/>
+      <c r="C39" s="16" t="n"/>
+      <c r="D39" s="17" t="n"/>
+      <c r="E39" s="16" t="n"/>
+      <c r="F39" s="15" t="n"/>
+      <c r="G39" s="16" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="n"/>
-      <c r="B40" s="11" t="n"/>
-      <c r="C40" s="11" t="n"/>
-      <c r="D40" s="11" t="n"/>
-      <c r="E40" s="11" t="n"/>
-      <c r="F40" s="11" t="n"/>
-      <c r="G40" s="11" t="n"/>
+      <c r="A40" s="15" t="n"/>
+      <c r="B40" s="15" t="n"/>
+      <c r="C40" s="16" t="n"/>
+      <c r="D40" s="17" t="n"/>
+      <c r="E40" s="16" t="n"/>
+      <c r="F40" s="15" t="n"/>
+      <c r="G40" s="16" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="n"/>
-      <c r="B41" s="11" t="n"/>
-      <c r="C41" s="11" t="n"/>
-      <c r="D41" s="11" t="n"/>
-      <c r="E41" s="11" t="n"/>
-      <c r="F41" s="11" t="n"/>
-      <c r="G41" s="11" t="n"/>
+      <c r="A41" s="15" t="n"/>
+      <c r="B41" s="15" t="n"/>
+      <c r="C41" s="16" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="16" t="n"/>
+      <c r="F41" s="15" t="n"/>
+      <c r="G41" s="16" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="n"/>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="11" t="n"/>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="11" t="n"/>
-      <c r="G42" s="11" t="n"/>
+      <c r="A42" s="15" t="n"/>
+      <c r="B42" s="15" t="n"/>
+      <c r="C42" s="16" t="n"/>
+      <c r="D42" s="17" t="n"/>
+      <c r="E42" s="16" t="n"/>
+      <c r="F42" s="15" t="n"/>
+      <c r="G42" s="16" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="n"/>
+      <c r="B43" s="15" t="n"/>
+      <c r="C43" s="16" t="n"/>
+      <c r="D43" s="17" t="n"/>
+      <c r="E43" s="16" t="n"/>
+      <c r="F43" s="15" t="n"/>
+      <c r="G43" s="16" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="n"/>
+      <c r="B44" s="15" t="n"/>
+      <c r="C44" s="16" t="n"/>
+      <c r="D44" s="17" t="n"/>
+      <c r="E44" s="16" t="n"/>
+      <c r="F44" s="15" t="n"/>
+      <c r="G44" s="16" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A7:G7"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="F8:F42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Choose one of: yes, no" type="list">
-      <formula1>"yes,no"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E8:E42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Out of range" error="Enter a whole number from 1 to 5." type="whole" operator="between">
+    <dataValidation sqref="E5:E44" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Out of range" error="Enter a whole number from 1 to 5." promptTitle="Rate 1 to 5" prompt="How much this blocks everything else" type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
-    <dataValidation sqref="G8:G42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Out of range" error="Enter a whole number from 1 to 5." type="whole" operator="between">
+    <dataValidation sqref="F5:F44" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Choose one of: yes, no" promptTitle="Pick from the list" prompt="Could software or a system do this?" type="list">
+      <formula1>"yes,no"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G5:G44" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Out of range" error="Enter a whole number from 1 to 5." promptTitle="Rate 1 to 5" prompt="1 is trivial, 5 is hard" type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
